--- a/projects/KE_Kapiti_Eddy_July/data/Kapiti Biodiversity and Plants Cover_EC Tower_April 2026+JH.xlsx
+++ b/projects/KE_Kapiti_Eddy_July/data/Kapiti Biodiversity and Plants Cover_EC Tower_April 2026+JH.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JHawkins\Documents\Github\Soil.C.modelling\Kapiti.soil.C\projects\KE_Kapiti_Eddy_July\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hawkj\Documents\Github\L-DNDC\Landscape-DNDC\projects\KE_Kapiti_Eddy_July\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9922F47-26CE-435E-9FB7-70A9546AAB5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" firstSheet="1" activeTab="5" xr2:uid="{5B3FAE64-1144-45E6-9D3C-23D2B8568905}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="9" xr2:uid="{5B3FAE64-1144-45E6-9D3C-23D2B8568905}"/>
   </bookViews>
   <sheets>
     <sheet name="EC Tower" sheetId="1" r:id="rId1"/>
@@ -1235,17 +1235,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82D3C29E-4AF9-4604-8CFA-B0C45CE17CDA}">
   <dimension ref="A1:U335"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.42578125" customWidth="1"/>
-    <col min="3" max="3" width="11.85546875" customWidth="1"/>
-    <col min="5" max="5" width="25.85546875" customWidth="1"/>
-    <col min="6" max="6" width="17.42578125" customWidth="1"/>
-    <col min="7" max="8" width="18.140625" customWidth="1"/>
+    <col min="1" max="1" width="16.44140625" customWidth="1"/>
+    <col min="3" max="3" width="11.88671875" customWidth="1"/>
+    <col min="5" max="5" width="25.88671875" customWidth="1"/>
+    <col min="6" max="6" width="17.44140625" customWidth="1"/>
+    <col min="7" max="8" width="18.109375" customWidth="1"/>
     <col min="9" max="9" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1310,7 +1310,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A2" s="5">
         <v>46120</v>
       </c>
@@ -1368,7 +1368,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A3" s="5">
         <v>46120</v>
       </c>
@@ -1417,7 +1417,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A4" s="5">
         <v>46120</v>
       </c>
@@ -1466,7 +1466,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A5" s="5">
         <v>46120</v>
       </c>
@@ -1515,7 +1515,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A6" s="5">
         <v>46120</v>
       </c>
@@ -1564,7 +1564,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A7" s="5">
         <v>46120</v>
       </c>
@@ -1613,7 +1613,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A8" s="5">
         <v>46120</v>
       </c>
@@ -1658,7 +1658,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A9" s="5">
         <v>46120</v>
       </c>
@@ -1707,7 +1707,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A10" s="5">
         <v>46120</v>
       </c>
@@ -1756,7 +1756,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A11" s="5">
         <v>46120</v>
       </c>
@@ -1802,7 +1802,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A12" s="5">
         <v>46120</v>
       </c>
@@ -1851,7 +1851,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A13" s="5">
         <v>46120</v>
       </c>
@@ -1900,7 +1900,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A14" s="5">
         <v>46120</v>
       </c>
@@ -1927,7 +1927,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A15" s="5">
         <v>46120</v>
       </c>
@@ -1976,7 +1976,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A16" s="5">
         <v>46120</v>
       </c>
@@ -2025,7 +2025,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A17" s="5">
         <v>46120</v>
       </c>
@@ -2074,7 +2074,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A18" s="5">
         <v>46120</v>
       </c>
@@ -2129,7 +2129,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A19" s="5">
         <v>46120</v>
       </c>
@@ -2178,7 +2178,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A20" s="5">
         <v>46120</v>
       </c>
@@ -2227,7 +2227,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A21" s="5">
         <v>46120</v>
       </c>
@@ -2272,7 +2272,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A22" s="5">
         <v>46120</v>
       </c>
@@ -2321,7 +2321,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A23" s="5">
         <v>46120</v>
       </c>
@@ -2367,7 +2367,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A24" s="5">
         <v>46120</v>
       </c>
@@ -2394,7 +2394,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A25" s="5">
         <v>46120</v>
       </c>
@@ -2443,7 +2443,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A26" s="5">
         <v>46120</v>
       </c>
@@ -2489,7 +2489,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A27" s="5">
         <v>46120</v>
       </c>
@@ -2538,7 +2538,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A28" s="5">
         <v>46120</v>
       </c>
@@ -2587,7 +2587,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A29" s="5">
         <v>46120</v>
       </c>
@@ -2636,7 +2636,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A30" s="5">
         <v>46120</v>
       </c>
@@ -2682,7 +2682,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A31" s="5">
         <v>46120</v>
       </c>
@@ -2731,7 +2731,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A32" s="5">
         <v>46120</v>
       </c>
@@ -2780,7 +2780,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="33" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A33" s="5">
         <v>46120</v>
       </c>
@@ -2829,7 +2829,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="34" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A34" s="5">
         <v>46120</v>
       </c>
@@ -2856,7 +2856,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="35" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A35" s="5">
         <v>46120</v>
       </c>
@@ -2908,7 +2908,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="36" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A36" s="5">
         <v>46120</v>
       </c>
@@ -2957,7 +2957,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="37" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A37" s="5">
         <v>46120</v>
       </c>
@@ -3012,7 +3012,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="38" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A38" s="5">
         <v>46120</v>
       </c>
@@ -3061,7 +3061,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="39" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A39" s="5">
         <v>46120</v>
       </c>
@@ -3110,7 +3110,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="40" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A40" s="5">
         <v>46120</v>
       </c>
@@ -3159,7 +3159,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="41" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A41" s="5">
         <v>46120</v>
       </c>
@@ -3192,7 +3192,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="42" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A42" s="5">
         <v>46120</v>
       </c>
@@ -3241,7 +3241,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="43" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A43" s="5">
         <v>46120</v>
       </c>
@@ -3290,7 +3290,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="44" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A44" s="5">
         <v>46120</v>
       </c>
@@ -3337,7 +3337,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="45" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A45" s="5">
         <v>46120</v>
       </c>
@@ -3386,7 +3386,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="46" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A46" s="5">
         <v>46120</v>
       </c>
@@ -3435,7 +3435,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="47" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A47" s="5">
         <v>46120</v>
       </c>
@@ -3468,7 +3468,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="48" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A48" s="5">
         <v>46120</v>
       </c>
@@ -3517,7 +3517,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="49" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A49" s="5">
         <v>46120</v>
       </c>
@@ -3569,7 +3569,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="50" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A50" s="5">
         <v>46120</v>
       </c>
@@ -3618,7 +3618,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="51" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A51" s="5">
         <v>46120</v>
       </c>
@@ -3673,7 +3673,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="52" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A52" s="5">
         <v>46120</v>
       </c>
@@ -3703,7 +3703,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A53" s="5">
         <v>46120</v>
       </c>
@@ -3749,7 +3749,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="54" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A54" s="5">
         <v>46120</v>
       </c>
@@ -3796,7 +3796,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="55" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A55" s="5">
         <v>46120</v>
       </c>
@@ -3845,7 +3845,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="56" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A56" s="5">
         <v>46120</v>
       </c>
@@ -3891,7 +3891,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="57" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A57" s="5">
         <v>46120</v>
       </c>
@@ -3940,7 +3940,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="58" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A58" s="5">
         <v>46120</v>
       </c>
@@ -3967,7 +3967,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="59" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A59" s="5">
         <v>46120</v>
       </c>
@@ -4016,7 +4016,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="60" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A60" s="5">
         <v>46120</v>
       </c>
@@ -4052,7 +4052,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A61" s="5">
         <v>46120</v>
       </c>
@@ -4098,7 +4098,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="62" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A62" s="5">
         <v>46120</v>
       </c>
@@ -4147,7 +4147,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="63" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A63" s="5">
         <v>46120</v>
       </c>
@@ -4196,7 +4196,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="64" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A64" s="5">
         <v>46120</v>
       </c>
@@ -4223,7 +4223,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="65" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A65" s="5">
         <v>46120</v>
       </c>
@@ -4265,7 +4265,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="66" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A66" s="5">
         <v>46120</v>
       </c>
@@ -4314,7 +4314,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="67" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A67" s="5">
         <v>46120</v>
       </c>
@@ -4363,7 +4363,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="68" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A68" s="5">
         <v>46120</v>
       </c>
@@ -4412,7 +4412,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="69" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A69" s="5">
         <v>46120</v>
       </c>
@@ -4439,7 +4439,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="70" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A70" s="5">
         <v>46120</v>
       </c>
@@ -4488,7 +4488,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="71" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A71" s="5">
         <v>46120</v>
       </c>
@@ -4534,7 +4534,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="72" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A72" s="5">
         <v>46120</v>
       </c>
@@ -4583,7 +4583,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="73" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A73" s="5">
         <v>46120</v>
       </c>
@@ -4632,7 +4632,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="74" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A74" s="5">
         <v>46120</v>
       </c>
@@ -4678,7 +4678,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="75" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A75" s="5">
         <v>46120</v>
       </c>
@@ -4724,7 +4724,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="76" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A76" s="5">
         <v>46120</v>
       </c>
@@ -4773,7 +4773,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="77" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A77" s="5">
         <v>46120</v>
       </c>
@@ -4822,7 +4822,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="78" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A78" s="5">
         <v>46120</v>
       </c>
@@ -4871,7 +4871,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="79" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A79" s="5">
         <v>46120</v>
       </c>
@@ -4920,7 +4920,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="80" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A80" s="5">
         <v>46120</v>
       </c>
@@ -4947,7 +4947,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="81" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A81" s="5">
         <v>46120</v>
       </c>
@@ -4996,7 +4996,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="82" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A82" s="5">
         <v>46120</v>
       </c>
@@ -5045,7 +5045,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="83" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A83" s="5">
         <v>46120</v>
       </c>
@@ -5094,7 +5094,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="84" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A84" s="5">
         <v>46120</v>
       </c>
@@ -5143,7 +5143,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="85" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A85" s="5">
         <v>46120</v>
       </c>
@@ -5192,7 +5192,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="86" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A86" s="5">
         <v>46120</v>
       </c>
@@ -5234,7 +5234,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="87" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A87" s="5">
         <v>46120</v>
       </c>
@@ -5283,7 +5283,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="88" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A88" s="5">
         <v>46120</v>
       </c>
@@ -5332,7 +5332,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="89" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A89" s="5">
         <v>46120</v>
       </c>
@@ -5378,7 +5378,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="90" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A90" s="5">
         <v>46120</v>
       </c>
@@ -5405,7 +5405,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="91" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A91" s="5">
         <v>46120</v>
       </c>
@@ -5454,7 +5454,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="92" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A92" s="5">
         <v>46120</v>
       </c>
@@ -5503,7 +5503,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="93" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A93" s="5">
         <v>46120</v>
       </c>
@@ -5552,7 +5552,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="94" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A94" s="5">
         <v>46120</v>
       </c>
@@ -5598,7 +5598,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="95" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A95" s="5">
         <v>46120</v>
       </c>
@@ -5647,7 +5647,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="96" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A96" s="5">
         <v>46120</v>
       </c>
@@ -5696,7 +5696,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="97" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A97" s="5">
         <v>46120</v>
       </c>
@@ -5745,7 +5745,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="98" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A98" s="5">
         <v>46120</v>
       </c>
@@ -5787,7 +5787,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="99" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A99" s="5">
         <v>46120</v>
       </c>
@@ -5836,7 +5836,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="100" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A100" s="5">
         <v>46120</v>
       </c>
@@ -5863,7 +5863,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="101" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A101" s="5">
         <v>46120</v>
       </c>
@@ -5912,7 +5912,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="102" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A102" s="5">
         <v>46120</v>
       </c>
@@ -5961,7 +5961,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="103" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A103" s="5">
         <v>46120</v>
       </c>
@@ -6007,7 +6007,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="104" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A104" s="5">
         <v>46120</v>
       </c>
@@ -6056,7 +6056,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="105" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A105" s="5">
         <v>46120</v>
       </c>
@@ -6105,7 +6105,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="106" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A106" s="5">
         <v>46120</v>
       </c>
@@ -6154,7 +6154,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="107" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A107" s="5">
         <v>46120</v>
       </c>
@@ -6203,7 +6203,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="108" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A108" s="5">
         <v>46120</v>
       </c>
@@ -6252,7 +6252,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="109" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A109" s="5">
         <v>46120</v>
       </c>
@@ -6301,7 +6301,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="110" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A110" s="5">
         <v>46120</v>
       </c>
@@ -6343,7 +6343,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="111" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A111" s="5">
         <v>46120</v>
       </c>
@@ -6392,7 +6392,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="112" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A112" s="5">
         <v>46120</v>
       </c>
@@ -6437,7 +6437,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="113" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A113" s="5">
         <v>46120</v>
       </c>
@@ -6483,7 +6483,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="114" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A114" s="5">
         <v>46120</v>
       </c>
@@ -6510,7 +6510,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="115" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A115" s="5">
         <v>46120</v>
       </c>
@@ -6559,7 +6559,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="116" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A116" s="5">
         <v>46120</v>
       </c>
@@ -6608,7 +6608,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="117" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A117" s="5">
         <v>46120</v>
       </c>
@@ -6657,7 +6657,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="118" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A118" s="5">
         <v>46120</v>
       </c>
@@ -6706,7 +6706,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="119" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A119" s="5">
         <v>46120</v>
       </c>
@@ -6755,7 +6755,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="120" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A120" s="5">
         <v>46120</v>
       </c>
@@ -6800,7 +6800,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="121" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A121" s="5">
         <v>46120</v>
       </c>
@@ -6849,7 +6849,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="122" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A122" s="5">
         <v>46120</v>
       </c>
@@ -6898,7 +6898,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="123" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A123" s="5">
         <v>46120</v>
       </c>
@@ -6943,7 +6943,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="124" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A124" s="5">
         <v>46120</v>
       </c>
@@ -6998,7 +6998,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="125" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A125" s="5">
         <v>46120</v>
       </c>
@@ -7025,7 +7025,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="126" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A126" s="5">
         <v>46120</v>
       </c>
@@ -7074,7 +7074,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="127" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A127" s="5">
         <v>46120</v>
       </c>
@@ -7129,7 +7129,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="128" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A128" s="5">
         <v>46120</v>
       </c>
@@ -7178,7 +7178,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="129" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A129" s="5">
         <v>46120</v>
       </c>
@@ -7227,7 +7227,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="130" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A130" s="5">
         <v>46120</v>
       </c>
@@ -7276,7 +7276,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="131" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A131" s="5">
         <v>46120</v>
       </c>
@@ -7325,7 +7325,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="132" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A132" s="5">
         <v>46120</v>
       </c>
@@ -7374,7 +7374,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="133" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A133" s="5">
         <v>46120</v>
       </c>
@@ -7423,7 +7423,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="134" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A134" s="5">
         <v>46120</v>
       </c>
@@ -7472,7 +7472,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="135" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A135" s="5">
         <v>46120</v>
       </c>
@@ -7521,7 +7521,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="136" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A136" s="5">
         <v>46120</v>
       </c>
@@ -7566,7 +7566,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="137" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A137" s="5">
         <v>46120</v>
       </c>
@@ -7615,7 +7615,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="138" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A138" s="5">
         <v>46120</v>
       </c>
@@ -7664,7 +7664,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="139" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A139" s="5">
         <v>46120</v>
       </c>
@@ -7691,7 +7691,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="140" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A140" s="5">
         <v>46120</v>
       </c>
@@ -7740,7 +7740,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="141" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A141" s="5">
         <v>46120</v>
       </c>
@@ -7789,7 +7789,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="142" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A142" s="5">
         <v>46120</v>
       </c>
@@ -7828,7 +7828,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A143" s="5">
         <v>46120</v>
       </c>
@@ -7877,7 +7877,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="144" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A144" s="5">
         <v>46120</v>
       </c>
@@ -7926,7 +7926,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="145" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A145" s="5">
         <v>46120</v>
       </c>
@@ -7975,7 +7975,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="146" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A146" s="5">
         <v>46120</v>
       </c>
@@ -8024,7 +8024,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="147" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A147" s="5">
         <v>46120</v>
       </c>
@@ -8073,7 +8073,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="148" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A148" s="5">
         <v>46120</v>
       </c>
@@ -8122,7 +8122,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="149" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A149" s="5">
         <v>46120</v>
       </c>
@@ -8171,7 +8171,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="150" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A150" s="5">
         <v>46120</v>
       </c>
@@ -8216,7 +8216,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="151" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A151" s="5">
         <v>46120</v>
       </c>
@@ -8265,7 +8265,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="152" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A152" s="5">
         <v>46120</v>
       </c>
@@ -8292,7 +8292,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="153" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A153" s="5">
         <v>46120</v>
       </c>
@@ -8341,7 +8341,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="154" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A154" s="5">
         <v>46120</v>
       </c>
@@ -8390,7 +8390,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="155" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A155" s="5">
         <v>46120</v>
       </c>
@@ -8439,7 +8439,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="156" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A156" s="5">
         <v>46120</v>
       </c>
@@ -8488,7 +8488,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="157" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A157" s="5">
         <v>46120</v>
       </c>
@@ -8524,7 +8524,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="158" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A158" s="5">
         <v>46120</v>
       </c>
@@ -8573,7 +8573,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="159" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A159" s="5">
         <v>46120</v>
       </c>
@@ -8618,7 +8618,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="160" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A160" s="5">
         <v>46120</v>
       </c>
@@ -8654,7 +8654,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="161" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A161" s="5">
         <v>46120</v>
       </c>
@@ -8709,7 +8709,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="162" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A162" s="5">
         <v>46120</v>
       </c>
@@ -8758,7 +8758,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="163" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A163" s="5">
         <v>46120</v>
       </c>
@@ -8785,7 +8785,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="164" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A164" s="5">
         <v>46120</v>
       </c>
@@ -8834,7 +8834,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="165" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A165" s="5">
         <v>46120</v>
       </c>
@@ -8883,7 +8883,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="166" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A166" s="5">
         <v>46120</v>
       </c>
@@ -8910,7 +8910,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="167" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A167" s="5">
         <v>46120</v>
       </c>
@@ -8959,7 +8959,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="168" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A168" s="5">
         <v>46120</v>
       </c>
@@ -9008,7 +9008,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="169" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A169" s="5">
         <v>46120</v>
       </c>
@@ -9057,7 +9057,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="170" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A170" s="5">
         <v>46120</v>
       </c>
@@ -9106,7 +9106,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="171" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A171" s="5">
         <v>46120</v>
       </c>
@@ -9145,7 +9145,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="172" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A172" s="5">
         <v>46120</v>
       </c>
@@ -9190,7 +9190,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="173" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A173" s="5">
         <v>46120</v>
       </c>
@@ -9239,7 +9239,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="174" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A174" s="5">
         <v>46120</v>
       </c>
@@ -9266,7 +9266,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="175" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A175" s="5">
         <v>46120</v>
       </c>
@@ -9321,7 +9321,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="176" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A176" s="5">
         <v>46120</v>
       </c>
@@ -9370,7 +9370,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="177" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A177" s="5">
         <v>46120</v>
       </c>
@@ -9419,7 +9419,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="178" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A178" s="5">
         <v>46120</v>
       </c>
@@ -9468,7 +9468,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="179" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A179" s="5">
         <v>46120</v>
       </c>
@@ -9517,7 +9517,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="180" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A180" s="5">
         <v>46120</v>
       </c>
@@ -9566,7 +9566,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="181" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A181" s="5">
         <v>46120</v>
       </c>
@@ -9615,7 +9615,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="182" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A182" s="5">
         <v>46120</v>
       </c>
@@ -9664,7 +9664,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="183" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A183" s="5">
         <v>46120</v>
       </c>
@@ -9711,7 +9711,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="184" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A184" s="5">
         <v>46120</v>
       </c>
@@ -9738,7 +9738,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="185" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A185" s="5">
         <v>46120</v>
       </c>
@@ -9790,7 +9790,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="186" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A186" s="5">
         <v>46120</v>
       </c>
@@ -9839,7 +9839,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="187" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A187" s="5">
         <v>46120</v>
       </c>
@@ -9888,7 +9888,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="188" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A188" s="5">
         <v>46120</v>
       </c>
@@ -9937,7 +9937,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="189" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A189" s="5">
         <v>46120</v>
       </c>
@@ -9986,7 +9986,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="190" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A190" s="5">
         <v>46120</v>
       </c>
@@ -10035,7 +10035,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="191" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A191" s="5">
         <v>46120</v>
       </c>
@@ -10084,7 +10084,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="192" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A192" s="5">
         <v>46120</v>
       </c>
@@ -10131,7 +10131,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="193" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A193" s="5">
         <v>46120</v>
       </c>
@@ -10180,7 +10180,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="194" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A194" s="5">
         <v>46120</v>
       </c>
@@ -10229,7 +10229,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="195" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A195" s="5">
         <v>46120</v>
       </c>
@@ -10256,7 +10256,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="196" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A196" s="5">
         <v>46120</v>
       </c>
@@ -10305,7 +10305,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="197" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A197" s="5">
         <v>46120</v>
       </c>
@@ -10354,7 +10354,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="198" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A198" s="5">
         <v>46120</v>
       </c>
@@ -10403,7 +10403,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="199" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A199" s="5">
         <v>46120</v>
       </c>
@@ -10452,7 +10452,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="200" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A200" s="5">
         <v>46120</v>
       </c>
@@ -10501,7 +10501,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="201" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A201" s="5">
         <v>46120</v>
       </c>
@@ -10550,7 +10550,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="202" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A202" s="5">
         <v>46120</v>
       </c>
@@ -10599,7 +10599,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="203" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A203" s="5">
         <v>46120</v>
       </c>
@@ -10646,7 +10646,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="204" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A204" s="5">
         <v>46120</v>
       </c>
@@ -10695,7 +10695,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="205" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A205" s="5">
         <v>46120</v>
       </c>
@@ -10740,7 +10740,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="206" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A206" s="5">
         <v>46120</v>
       </c>
@@ -10789,7 +10789,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="207" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A207" s="5">
         <v>46120</v>
       </c>
@@ -10838,7 +10838,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="208" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A208" s="5">
         <v>46120</v>
       </c>
@@ -10865,7 +10865,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="209" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A209" s="5">
         <v>46120</v>
       </c>
@@ -10917,7 +10917,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="210" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A210" s="5">
         <v>46120</v>
       </c>
@@ -10966,7 +10966,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="211" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A211" s="5">
         <v>46120</v>
       </c>
@@ -11015,7 +11015,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="212" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A212" s="5">
         <v>46120</v>
       </c>
@@ -11070,7 +11070,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="213" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A213" s="5">
         <v>46120</v>
       </c>
@@ -11119,7 +11119,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="214" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A214" s="5">
         <v>46120</v>
       </c>
@@ -11168,7 +11168,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="215" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A215" s="5">
         <v>46120</v>
       </c>
@@ -11217,7 +11217,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="216" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A216" s="5">
         <v>46120</v>
       </c>
@@ -11262,7 +11262,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="217" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A217" s="5">
         <v>46120</v>
       </c>
@@ -11311,7 +11311,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="218" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A218" s="5">
         <v>46120</v>
       </c>
@@ -11360,7 +11360,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="219" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A219" s="5">
         <v>46120</v>
       </c>
@@ -11409,7 +11409,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="220" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A220" s="5">
         <v>46120</v>
       </c>
@@ -11458,7 +11458,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="221" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A221" s="5">
         <v>46120</v>
       </c>
@@ -11507,7 +11507,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="222" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A222" s="5">
         <v>46120</v>
       </c>
@@ -11556,7 +11556,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="223" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A223" s="5">
         <v>46120</v>
       </c>
@@ -11583,7 +11583,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="224" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A224" s="5">
         <v>46120</v>
       </c>
@@ -11632,7 +11632,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="225" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A225" s="5">
         <v>46120</v>
       </c>
@@ -11681,7 +11681,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="226" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A226" s="5">
         <v>46120</v>
       </c>
@@ -11730,7 +11730,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="227" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A227" s="5">
         <v>46120</v>
       </c>
@@ -11779,7 +11779,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="228" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A228" s="5">
         <v>46120</v>
       </c>
@@ -11834,7 +11834,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="229" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A229" s="5">
         <v>46120</v>
       </c>
@@ -11883,7 +11883,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="230" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A230" s="5">
         <v>46120</v>
       </c>
@@ -11932,7 +11932,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="231" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A231" s="5">
         <v>46120</v>
       </c>
@@ -11981,7 +11981,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="232" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A232" s="5">
         <v>46120</v>
       </c>
@@ -12030,7 +12030,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="233" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A233" s="5">
         <v>46120</v>
       </c>
@@ -12057,7 +12057,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="234" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A234" s="5">
         <v>46120</v>
       </c>
@@ -12106,7 +12106,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="235" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A235" s="5">
         <v>46120</v>
       </c>
@@ -12155,7 +12155,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="236" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A236" s="5">
         <v>46120</v>
       </c>
@@ -12204,7 +12204,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="237" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A237" s="5">
         <v>46120</v>
       </c>
@@ -12253,7 +12253,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="238" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A238" s="5">
         <v>46120</v>
       </c>
@@ -12308,7 +12308,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="239" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A239" s="5">
         <v>46120</v>
       </c>
@@ -12350,7 +12350,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="240" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A240" s="5">
         <v>46120</v>
       </c>
@@ -12399,7 +12399,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="241" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A241" s="5">
         <v>46120</v>
       </c>
@@ -12448,7 +12448,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="242" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A242" s="5">
         <v>46120</v>
       </c>
@@ -12497,7 +12497,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="243" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A243" s="5">
         <v>46120</v>
       </c>
@@ -12546,7 +12546,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="244" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A244" s="5">
         <v>46120</v>
       </c>
@@ -12573,7 +12573,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="245" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A245" s="5">
         <v>46120</v>
       </c>
@@ -12622,7 +12622,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="246" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A246" s="5">
         <v>46120</v>
       </c>
@@ -12671,7 +12671,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="247" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A247" s="5">
         <v>46120</v>
       </c>
@@ -12720,7 +12720,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="248" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A248" s="5">
         <v>46120</v>
       </c>
@@ -12769,7 +12769,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="249" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A249" s="5">
         <v>46120</v>
       </c>
@@ -12814,7 +12814,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="250" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A250" s="5">
         <v>46120</v>
       </c>
@@ -12856,7 +12856,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="251" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A251" s="5">
         <v>46120</v>
       </c>
@@ -12905,7 +12905,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="252" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A252" s="5">
         <v>46120</v>
       </c>
@@ -12954,7 +12954,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="253" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A253" s="5">
         <v>46120</v>
       </c>
@@ -13003,7 +13003,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="254" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A254" s="5">
         <v>46120</v>
       </c>
@@ -13048,7 +13048,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="255" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A255" s="5">
         <v>46120</v>
       </c>
@@ -13097,7 +13097,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="256" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A256" s="5">
         <v>46120</v>
       </c>
@@ -13143,7 +13143,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="257" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A257" s="5">
         <v>46120</v>
       </c>
@@ -13192,7 +13192,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="258" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A258" s="5">
         <v>46120</v>
       </c>
@@ -13219,7 +13219,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="259" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A259" s="5">
         <v>46120</v>
       </c>
@@ -13268,7 +13268,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="260" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A260" s="5">
         <v>46120</v>
       </c>
@@ -13317,7 +13317,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="261" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A261" s="5">
         <v>46120</v>
       </c>
@@ -13366,7 +13366,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="262" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A262" s="5">
         <v>46120</v>
       </c>
@@ -13421,7 +13421,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="263" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A263" s="5">
         <v>46120</v>
       </c>
@@ -13470,7 +13470,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="264" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A264" s="5">
         <v>46120</v>
       </c>
@@ -13519,7 +13519,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="265" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A265" s="5">
         <v>46120</v>
       </c>
@@ -13565,7 +13565,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="266" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A266" s="5">
         <v>46120</v>
       </c>
@@ -13592,7 +13592,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="267" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A267" s="5">
         <v>46120</v>
       </c>
@@ -13641,7 +13641,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="268" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A268" s="5">
         <v>46120</v>
       </c>
@@ -13690,7 +13690,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="269" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A269" s="5">
         <v>46120</v>
       </c>
@@ -13739,7 +13739,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="270" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A270" s="5">
         <v>46120</v>
       </c>
@@ -13788,7 +13788,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="271" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A271" s="5">
         <v>46120</v>
       </c>
@@ -13843,7 +13843,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="272" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A272" s="5">
         <v>46120</v>
       </c>
@@ -13892,7 +13892,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="273" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A273" s="5">
         <v>46120</v>
       </c>
@@ -13941,7 +13941,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="274" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A274" s="5">
         <v>46120</v>
       </c>
@@ -13988,7 +13988,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="275" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A275" s="5">
         <v>46120</v>
       </c>
@@ -14015,7 +14015,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="276" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A276" s="5">
         <v>46120</v>
       </c>
@@ -14064,7 +14064,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="277" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A277" s="5">
         <v>46120</v>
       </c>
@@ -14113,7 +14113,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="278" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A278" s="5">
         <v>46120</v>
       </c>
@@ -14162,7 +14162,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="279" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A279" s="5">
         <v>46120</v>
       </c>
@@ -14211,7 +14211,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="280" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A280" s="5">
         <v>46120</v>
       </c>
@@ -14260,7 +14260,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="281" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A281" s="5">
         <v>46120</v>
       </c>
@@ -14309,7 +14309,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="282" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A282" s="5">
         <v>46120</v>
       </c>
@@ -14364,7 +14364,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="283" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A283" s="5">
         <v>46120</v>
       </c>
@@ -14413,7 +14413,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="284" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A284" s="5">
         <v>46120</v>
       </c>
@@ -14462,7 +14462,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="285" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A285" s="5">
         <v>46120</v>
       </c>
@@ -14511,7 +14511,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="286" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A286" s="5">
         <v>46120</v>
       </c>
@@ -14538,7 +14538,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="287" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A287" s="5">
         <v>46120</v>
       </c>
@@ -14587,7 +14587,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="288" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A288" s="5">
         <v>46120</v>
       </c>
@@ -14636,7 +14636,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="289" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A289" s="5">
         <v>46120</v>
       </c>
@@ -14685,7 +14685,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="290" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A290" s="5">
         <v>46120</v>
       </c>
@@ -14740,7 +14740,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="291" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A291" s="5">
         <v>46120</v>
       </c>
@@ -14789,7 +14789,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="292" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A292" s="5">
         <v>46120</v>
       </c>
@@ -14836,7 +14836,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="293" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A293" s="5">
         <v>46120</v>
       </c>
@@ -14885,7 +14885,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="294" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A294" s="5">
         <v>46120</v>
       </c>
@@ -14934,7 +14934,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="295" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A295" s="5">
         <v>46120</v>
       </c>
@@ -14980,7 +14980,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="296" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A296" s="5">
         <v>46120</v>
       </c>
@@ -15010,7 +15010,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="297" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A297" s="5">
         <v>46120</v>
       </c>
@@ -15037,7 +15037,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="298" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A298" s="5">
         <v>46120</v>
       </c>
@@ -15086,7 +15086,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="299" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A299" s="5">
         <v>46120</v>
       </c>
@@ -15135,7 +15135,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="300" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A300" s="5">
         <v>46120</v>
       </c>
@@ -15182,7 +15182,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="301" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A301" s="5">
         <v>46120</v>
       </c>
@@ -15231,7 +15231,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="302" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A302" s="5">
         <v>46120</v>
       </c>
@@ -15277,7 +15277,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="303" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A303" s="5">
         <v>46120</v>
       </c>
@@ -15316,7 +15316,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="304" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A304" s="5">
         <v>46120</v>
       </c>
@@ -15371,7 +15371,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="305" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A305" s="5">
         <v>46120</v>
       </c>
@@ -15417,7 +15417,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="306" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A306" s="5">
         <v>46120</v>
       </c>
@@ -15466,7 +15466,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="307" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A307" s="5">
         <v>46120</v>
       </c>
@@ -15493,7 +15493,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="308" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A308" s="5">
         <v>46120</v>
       </c>
@@ -15542,7 +15542,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="309" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A309" s="5">
         <v>46120</v>
       </c>
@@ -15581,7 +15581,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="310" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A310" s="5">
         <v>46120</v>
       </c>
@@ -15630,7 +15630,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="311" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A311" s="5">
         <v>46120</v>
       </c>
@@ -15676,7 +15676,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="312" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A312" s="5">
         <v>46120</v>
       </c>
@@ -15725,7 +15725,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="313" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A313" s="5">
         <v>46120</v>
       </c>
@@ -15771,7 +15771,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="314" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A314" s="5">
         <v>46120</v>
       </c>
@@ -15820,7 +15820,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="315" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A315" s="5">
         <v>46120</v>
       </c>
@@ -15869,7 +15869,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="316" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A316" s="5">
         <v>46120</v>
       </c>
@@ -15896,7 +15896,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="317" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A317" s="5">
         <v>46120</v>
       </c>
@@ -15945,7 +15945,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="318" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A318" s="5">
         <v>46120</v>
       </c>
@@ -15994,7 +15994,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="319" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A319" s="5">
         <v>46120</v>
       </c>
@@ -16043,7 +16043,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="320" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A320" s="5">
         <v>46120</v>
       </c>
@@ -16090,7 +16090,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="321" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A321" s="5">
         <v>46120</v>
       </c>
@@ -16139,7 +16139,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="322" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A322" s="5">
         <v>46120</v>
       </c>
@@ -16186,7 +16186,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="323" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A323" s="5">
         <v>46120</v>
       </c>
@@ -16213,7 +16213,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="324" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A324" s="5">
         <v>46120</v>
       </c>
@@ -16260,7 +16260,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="325" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A325" s="5">
         <v>46120</v>
       </c>
@@ -16309,7 +16309,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="326" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A326" s="5">
         <v>46120</v>
       </c>
@@ -16364,7 +16364,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="327" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A327" s="5">
         <v>46120</v>
       </c>
@@ -16413,7 +16413,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="328" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A328" s="5">
         <v>46120</v>
       </c>
@@ -16459,7 +16459,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="329" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A329" s="5">
         <v>46120</v>
       </c>
@@ -16489,7 +16489,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="330" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A330" s="5">
         <v>46120</v>
       </c>
@@ -16535,7 +16535,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="331" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A331" s="5">
         <v>46120</v>
       </c>
@@ -16584,7 +16584,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="332" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A332" s="5">
         <v>46120</v>
       </c>
@@ -16611,7 +16611,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="333" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A333" s="5"/>
       <c r="I333" s="6"/>
       <c r="J333" s="7"/>
@@ -16624,10 +16624,10 @@
       <c r="Q333" s="6"/>
       <c r="R333" s="6"/>
     </row>
-    <row r="334" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A334" s="5"/>
     </row>
-    <row r="335" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A335" s="5"/>
     </row>
   </sheetData>
@@ -16638,24 +16638,24 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55B8416A-7BFD-4A28-8198-35D0340A2E6A}">
   <dimension ref="A1:A4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>191</v>
       </c>
@@ -16668,15 +16668,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11AAF763-B060-4F15-B7D2-F2A4CB5F604E}">
   <dimension ref="B1:O21"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="10" max="10" width="13.28515625" customWidth="1"/>
-    <col min="11" max="11" width="15.85546875" customWidth="1"/>
-    <col min="12" max="12" width="19.140625" customWidth="1"/>
-    <col min="13" max="13" width="26.85546875" customWidth="1"/>
+    <col min="10" max="10" width="13.33203125" customWidth="1"/>
+    <col min="11" max="11" width="15.88671875" customWidth="1"/>
+    <col min="12" max="12" width="19.109375" customWidth="1"/>
+    <col min="13" max="13" width="26.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B1" t="s">
         <v>193</v>
       </c>
@@ -16717,7 +16717,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B2">
         <v>1</v>
       </c>
@@ -16746,7 +16746,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="3" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B3">
         <v>2</v>
       </c>
@@ -16766,7 +16766,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="4" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B4">
         <v>3</v>
       </c>
@@ -16780,7 +16780,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="5" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B5">
         <v>4</v>
       </c>
@@ -16794,7 +16794,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="6" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B6">
         <v>5</v>
       </c>
@@ -16809,7 +16809,7 @@
       </c>
       <c r="N6" s="7"/>
     </row>
-    <row r="7" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B7">
         <v>6</v>
       </c>
@@ -16824,7 +16824,7 @@
       </c>
       <c r="N7" s="7"/>
     </row>
-    <row r="8" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B8">
         <v>7</v>
       </c>
@@ -16836,7 +16836,7 @@
       </c>
       <c r="N8" s="7"/>
     </row>
-    <row r="9" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B9">
         <v>8</v>
       </c>
@@ -16845,7 +16845,7 @@
       </c>
       <c r="N9" s="7"/>
     </row>
-    <row r="10" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B10">
         <v>9</v>
       </c>
@@ -16854,7 +16854,7 @@
       </c>
       <c r="N10" s="7"/>
     </row>
-    <row r="11" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B11">
         <v>10</v>
       </c>
@@ -16863,7 +16863,7 @@
       </c>
       <c r="N11" s="7"/>
     </row>
-    <row r="12" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B12">
         <v>1</v>
       </c>
@@ -16884,7 +16884,7 @@
       </c>
       <c r="N12" s="7"/>
     </row>
-    <row r="13" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:15" x14ac:dyDescent="0.3">
       <c r="C13">
         <v>2</v>
       </c>
@@ -16893,7 +16893,7 @@
       </c>
       <c r="N13" s="7"/>
     </row>
-    <row r="14" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:15" x14ac:dyDescent="0.3">
       <c r="C14">
         <v>3</v>
       </c>
@@ -16901,7 +16901,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="15" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:15" x14ac:dyDescent="0.3">
       <c r="C15">
         <v>4</v>
       </c>
@@ -16909,34 +16909,34 @@
         <v>228</v>
       </c>
     </row>
-    <row r="16" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:15" x14ac:dyDescent="0.3">
       <c r="M16" s="7" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="17" spans="12:14" x14ac:dyDescent="0.25">
+    <row r="17" spans="12:14" x14ac:dyDescent="0.3">
       <c r="M17" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="18" spans="12:14" x14ac:dyDescent="0.25">
+    <row r="18" spans="12:14" x14ac:dyDescent="0.3">
       <c r="L18" s="7"/>
       <c r="M18" s="7" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="19" spans="12:14" x14ac:dyDescent="0.25">
+    <row r="19" spans="12:14" x14ac:dyDescent="0.3">
       <c r="M19" s="7" t="s">
         <v>233</v>
       </c>
       <c r="N19" s="7"/>
     </row>
-    <row r="20" spans="12:14" x14ac:dyDescent="0.25">
+    <row r="20" spans="12:14" x14ac:dyDescent="0.3">
       <c r="M20" s="7" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="21" spans="12:14" x14ac:dyDescent="0.25">
+    <row r="21" spans="12:14" x14ac:dyDescent="0.3">
       <c r="M21" s="7" t="s">
         <v>238</v>
       </c>
@@ -16950,9 +16950,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7993D18-A363-45DA-8789-4889A5E255EB}">
   <dimension ref="A1:U11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:21" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>242</v>
       </c>
@@ -17017,7 +17017,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A2" s="5">
         <v>46120</v>
       </c>
@@ -17065,7 +17065,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A3" s="5">
         <v>46120</v>
       </c>
@@ -17113,7 +17113,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A4" s="5">
         <v>46120</v>
       </c>
@@ -17161,7 +17161,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A5" s="5">
         <v>46120</v>
       </c>
@@ -17209,7 +17209,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A6" s="5">
         <v>46120</v>
       </c>
@@ -17263,7 +17263,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A7" s="5">
         <v>46120</v>
       </c>
@@ -17311,7 +17311,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A8" s="5">
         <v>46120</v>
       </c>
@@ -17359,7 +17359,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A9" s="5">
         <v>46120</v>
       </c>
@@ -17407,7 +17407,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A10" s="5">
         <v>46120</v>
       </c>
@@ -17455,7 +17455,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A11" s="5">
         <v>46120</v>
       </c>
@@ -17489,12 +17489,12 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6509CDF-1315-42E7-8F44-0C7AAD273F43}">
   <dimension ref="A1:U16"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="6" max="6" width="15.42578125" customWidth="1"/>
+    <col min="6" max="6" width="15.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>242</v>
       </c>
@@ -17559,7 +17559,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A2" s="5">
         <v>46120</v>
       </c>
@@ -17610,7 +17610,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A3" s="5">
         <v>46120</v>
       </c>
@@ -17658,7 +17658,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A4" s="5">
         <v>46120</v>
       </c>
@@ -17706,7 +17706,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A5" s="5">
         <v>46120</v>
       </c>
@@ -17760,7 +17760,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A6" s="5">
         <v>46120</v>
       </c>
@@ -17808,7 +17808,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A7" s="5">
         <v>46120</v>
       </c>
@@ -17856,7 +17856,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A8" s="5">
         <v>46120</v>
       </c>
@@ -17904,7 +17904,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A9" s="5">
         <v>46120</v>
       </c>
@@ -17948,7 +17948,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A10" s="5">
         <v>46120</v>
       </c>
@@ -17996,7 +17996,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A11" s="5">
         <v>46120</v>
       </c>
@@ -18044,7 +18044,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A12" s="5">
         <v>46120</v>
       </c>
@@ -18092,7 +18092,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A13" s="5">
         <v>46120</v>
       </c>
@@ -18140,7 +18140,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A14" s="5">
         <v>46120</v>
       </c>
@@ -18188,7 +18188,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A15" s="5">
         <v>46120</v>
       </c>
@@ -18236,7 +18236,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A16" s="5">
         <v>46120</v>
       </c>
@@ -18270,9 +18270,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{337AB0DD-710A-48C1-A942-DFDF5C694276}">
   <dimension ref="A1:U14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:21" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>242</v>
       </c>
@@ -18337,7 +18337,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A2" s="5">
         <v>46120</v>
       </c>
@@ -18385,7 +18385,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A3" s="5">
         <v>46120</v>
       </c>
@@ -18433,7 +18433,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A4" s="5">
         <v>46120</v>
       </c>
@@ -18481,7 +18481,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A5" s="5">
         <v>46120</v>
       </c>
@@ -18529,7 +18529,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A6" s="5">
         <v>46120</v>
       </c>
@@ -18577,7 +18577,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A7" s="5">
         <v>46120</v>
       </c>
@@ -18625,7 +18625,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A8" s="5">
         <v>46120</v>
       </c>
@@ -18673,7 +18673,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A9" s="5">
         <v>46120</v>
       </c>
@@ -18719,7 +18719,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A10" s="5">
         <v>46120</v>
       </c>
@@ -18767,7 +18767,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A11" s="5">
         <v>46120</v>
       </c>
@@ -18811,7 +18811,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A12" s="5">
         <v>46120</v>
       </c>
@@ -18859,7 +18859,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A13" s="5">
         <v>46120</v>
       </c>
@@ -18907,7 +18907,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A14" s="5">
         <v>46120</v>
       </c>
@@ -18941,9 +18941,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A05E2CD3-96F9-4211-996F-6BE63534A94E}">
   <dimension ref="A1:U12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:21" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>242</v>
       </c>
@@ -19008,7 +19008,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A2" s="5">
         <v>46120</v>
       </c>
@@ -19059,7 +19059,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A3" s="5">
         <v>46120</v>
       </c>
@@ -19107,7 +19107,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A4" s="5">
         <v>46120</v>
       </c>
@@ -19155,7 +19155,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A5" s="5">
         <v>46120</v>
       </c>
@@ -19203,7 +19203,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A6" s="5">
         <v>46120</v>
       </c>
@@ -19251,7 +19251,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A7" s="5">
         <v>46120</v>
       </c>
@@ -19299,7 +19299,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A8" s="5">
         <v>46120</v>
       </c>
@@ -19347,7 +19347,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A9" s="5">
         <v>46120</v>
       </c>
@@ -19393,7 +19393,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A10" s="5">
         <v>46120</v>
       </c>
@@ -19441,7 +19441,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A11" s="5">
         <v>46120</v>
       </c>
@@ -19489,7 +19489,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A12" s="5">
         <v>46120</v>
       </c>
@@ -19523,9 +19523,9 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{560EF806-B1EC-46A4-BC1F-0DCFD643143D}">
   <dimension ref="A1:U11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:21" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>242</v>
       </c>
@@ -19590,7 +19590,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A2" s="5">
         <v>46120</v>
       </c>
@@ -19644,7 +19644,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A3" s="5">
         <v>46120</v>
       </c>
@@ -19692,7 +19692,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A4" s="5">
         <v>46120</v>
       </c>
@@ -19740,7 +19740,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A5" s="5">
         <v>46120</v>
       </c>
@@ -19788,7 +19788,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A6" s="5">
         <v>46120</v>
       </c>
@@ -19836,7 +19836,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A7" s="5">
         <v>46120</v>
       </c>
@@ -19884,7 +19884,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A8" s="5">
         <v>46120</v>
       </c>
@@ -19932,7 +19932,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A9" s="5">
         <v>46120</v>
       </c>
@@ -19980,7 +19980,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A10" s="5">
         <v>46120</v>
       </c>
@@ -20026,7 +20026,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A11" s="5">
         <v>46120</v>
       </c>
@@ -20060,9 +20060,9 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA0FD73B-20B3-4074-969A-084B773D458F}">
   <dimension ref="A1:S10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:19" ht="45" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -20121,7 +20121,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>19</v>
       </c>
@@ -20163,7 +20163,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>19</v>
       </c>
@@ -20205,7 +20205,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -20247,7 +20247,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -20295,7 +20295,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -20337,7 +20337,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>19</v>
       </c>
@@ -20379,7 +20379,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -20417,7 +20417,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>19</v>
       </c>
@@ -20459,7 +20459,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -20509,7 +20509,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8EC5221-F4CC-45B4-AD15-0CCD40AEB93A}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
